--- a/data-manipulation-scripts/sheets-cleanup/sheets/PINO GUIA 06_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PINO GUIA 06_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -44,12 +44,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>7893986239235</t>
-  </si>
-  <si>
-    <t>PINO GUIA TAMPA LATERAL  BIZ100 110/ POP100 110/ FAN</t>
   </si>
 </sst>
 </file>
@@ -402,29 +396,21 @@
       <c r="D6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -6369,20 +6355,14 @@
       <c r="C999" s="3"/>
       <c r="D999" s="3"/>
     </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A999">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A999">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
